--- a/Bibsam_tidskriftslistor/scifree_data_brill.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_brill.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_B8A85F4F591D7C17B25102653C0077E43A6883BB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B603BAA6-A26C-4704-B5B2-17F5B8BEEDC8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2B9BB0-6068-42DE-8F41-68B7E9AEFD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2156" uniqueCount="1089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2170" uniqueCount="1097">
   <si>
     <t>ISSN Electronic</t>
   </si>
@@ -64,9 +64,6 @@
     <t>African Journal of Legal Studies</t>
   </si>
   <si>
-    <t>African Yearbook of International Law Online / Annuaire Africain de droit international Online</t>
-  </si>
-  <si>
     <t>Afrika Focus</t>
   </si>
   <si>
@@ -151,9 +148,6 @@
     <t>Behaviour</t>
   </si>
   <si>
-    <t>Beijing International Review of Education</t>
-  </si>
-  <si>
     <t>Biblical Interpretation</t>
   </si>
   <si>
@@ -163,9 +157,6 @@
     <t>Bijdragen tot de Taal-, Land- en Volkenkunde / Journal of the Humanities and Social Sciences of Southeast Asia</t>
   </si>
   <si>
-    <t>Bridging Humanities</t>
-  </si>
-  <si>
     <t>Brill's Journal of Afroasiatic Languages and Linguistics</t>
   </si>
   <si>
@@ -637,9 +628,6 @@
     <t>Logos</t>
   </si>
   <si>
-    <t>Manusya: Journal of Humanities</t>
-  </si>
-  <si>
     <t>Matatu</t>
   </si>
   <si>
@@ -964,9 +952,6 @@
     <t>1708-7384</t>
   </si>
   <si>
-    <t>2211-6176</t>
-  </si>
-  <si>
     <t>2031-356X</t>
   </si>
   <si>
@@ -1051,9 +1036,6 @@
     <t>1568-539X</t>
   </si>
   <si>
-    <t>2590-2539</t>
-  </si>
-  <si>
     <t>1568-5152</t>
   </si>
   <si>
@@ -1063,9 +1045,6 @@
     <t>2213-4379</t>
   </si>
   <si>
-    <t>2542-5099</t>
-  </si>
-  <si>
     <t>1877-6930</t>
   </si>
   <si>
@@ -1510,9 +1489,6 @@
     <t>1571-8050</t>
   </si>
   <si>
-    <t xml:space="preserve">2666-318X </t>
-  </si>
-  <si>
     <t>1872-2636</t>
   </si>
   <si>
@@ -1537,9 +1513,6 @@
     <t>1878-4712</t>
   </si>
   <si>
-    <t>2665-9077</t>
-  </si>
-  <si>
     <t>1875-7421</t>
   </si>
   <si>
@@ -1864,9 +1837,6 @@
     <t>https://brill.com/ajls</t>
   </si>
   <si>
-    <t>https://brill.com/afyo</t>
-  </si>
-  <si>
     <t>https://brill.com/afoc</t>
   </si>
   <si>
@@ -1951,9 +1921,6 @@
     <t>https://brill.com/beh</t>
   </si>
   <si>
-    <t>https://brill.com/bire</t>
-  </si>
-  <si>
     <t>https://brill.com/bi</t>
   </si>
   <si>
@@ -1963,9 +1930,6 @@
     <t>https://brill.com/bki</t>
   </si>
   <si>
-    <t>https://brill.com/brhu</t>
-  </si>
-  <si>
     <t>https://brill.com/aall</t>
   </si>
   <si>
@@ -2437,9 +2401,6 @@
     <t>https://brill.com/logo</t>
   </si>
   <si>
-    <t>https://brill.com/mnya</t>
-  </si>
-  <si>
     <t>https://brill.com/mata</t>
   </si>
   <si>
@@ -2809,9 +2770,6 @@
     <t>https://brill.com/cvj</t>
   </si>
   <si>
-    <t xml:space="preserve">2949-7833 </t>
-  </si>
-  <si>
     <t>Dabir</t>
   </si>
   <si>
@@ -2908,9 +2866,6 @@
     <t>https://brill.com/jct</t>
   </si>
   <si>
-    <t xml:space="preserve">2773-2363 </t>
-  </si>
-  <si>
     <t>Journal of Digital Islamicate Research</t>
   </si>
   <si>
@@ -2944,9 +2899,6 @@
     <t>https://brill.com/jlso</t>
   </si>
   <si>
-    <t xml:space="preserve">2772-7882 </t>
-  </si>
-  <si>
     <t>Journal of Pacifism and Nonviolence</t>
   </si>
   <si>
@@ -2980,9 +2932,6 @@
     <t>https://brill.com/prot</t>
   </si>
   <si>
-    <t xml:space="preserve">2773-2142 </t>
-  </si>
-  <si>
     <t>Journal of Religious Minorities under Muslim Rule</t>
   </si>
   <si>
@@ -2998,9 +2947,6 @@
     <t>https://brill.com/rnd</t>
   </si>
   <si>
-    <t xml:space="preserve">2773-0840 </t>
-  </si>
-  <si>
     <t>Scottish Educational Review</t>
   </si>
   <si>
@@ -3085,15 +3031,6 @@
     <t>https://brill.com/ifam</t>
   </si>
   <si>
-    <t>2049-257X</t>
-  </si>
-  <si>
-    <t>Journal of Applied Animal Nutrition</t>
-  </si>
-  <si>
-    <t>https://brill.com/jaan</t>
-  </si>
-  <si>
     <t>2950-1229</t>
   </si>
   <si>
@@ -3163,15 +3100,6 @@
     <t>https://brill.com/mesr</t>
   </si>
   <si>
-    <t>2521-7038</t>
-  </si>
-  <si>
-    <t>Vienna Journal of East Asian Studies</t>
-  </si>
-  <si>
-    <t>https://brill.com/veas</t>
-  </si>
-  <si>
     <t>1875-0796</t>
   </si>
   <si>
@@ -3202,9 +3130,6 @@
     <t>https://brill.com/hlyu</t>
   </si>
   <si>
-    <t xml:space="preserve">3050-6107 </t>
-  </si>
-  <si>
     <t>Intercultural Dialogue</t>
   </si>
   <si>
@@ -3232,9 +3157,6 @@
     <t>https://brill.com/jbds</t>
   </si>
   <si>
-    <t xml:space="preserve">3050-5887 </t>
-  </si>
-  <si>
     <t>Journal of Hip-Hop and Education</t>
   </si>
   <si>
@@ -3287,6 +3209,108 @@
   </si>
   <si>
     <t>https://brill.com/sap</t>
+  </si>
+  <si>
+    <t>3050-760X</t>
+  </si>
+  <si>
+    <t>1110-8673</t>
+  </si>
+  <si>
+    <t>Alif: Journal of Comparative Poetics</t>
+  </si>
+  <si>
+    <t>https://brill.com/alif</t>
+  </si>
+  <si>
+    <t>3050-5046</t>
+  </si>
+  <si>
+    <t>Arab Yearbook of Public &amp; Private International Law, The</t>
+  </si>
+  <si>
+    <t>https://brill.com/aypp</t>
+  </si>
+  <si>
+    <t>2949-7833</t>
+  </si>
+  <si>
+    <t>3050-6107</t>
+  </si>
+  <si>
+    <t>1869-6945</t>
+  </si>
+  <si>
+    <t>International Journal of Food System Dynamics, The</t>
+  </si>
+  <si>
+    <t>https://brill.com/fsd</t>
+  </si>
+  <si>
+    <t>2589-0905</t>
+  </si>
+  <si>
+    <t>2589-0891</t>
+  </si>
+  <si>
+    <t>International Journal of Restorative Justice, The</t>
+  </si>
+  <si>
+    <t>https://brill.com/tij</t>
+  </si>
+  <si>
+    <t>3050-7197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Artificial Intelligence, Risk Regulation, Law, and Policy </t>
+  </si>
+  <si>
+    <t>https://brill.com/jair</t>
+  </si>
+  <si>
+    <t>2773-2363</t>
+  </si>
+  <si>
+    <t>3050-5887</t>
+  </si>
+  <si>
+    <t>2772-7882</t>
+  </si>
+  <si>
+    <t>2773-2142</t>
+  </si>
+  <si>
+    <t>2666-318X</t>
+  </si>
+  <si>
+    <t>3050-8088</t>
+  </si>
+  <si>
+    <t>Latin American and Caribbean Journal of International Law</t>
+  </si>
+  <si>
+    <t>https://brill.com/lacj</t>
+  </si>
+  <si>
+    <t>3050-8762</t>
+  </si>
+  <si>
+    <t>Malta Journal for Legal Studies</t>
+  </si>
+  <si>
+    <t>https://brill.com/mjls</t>
+  </si>
+  <si>
+    <t>3050-5631</t>
+  </si>
+  <si>
+    <t>New Zealand Yearbook of International Law Online</t>
+  </si>
+  <si>
+    <t>https://brill.com/nzyo</t>
+  </si>
+  <si>
+    <t>2773-0840</t>
   </si>
 </sst>
 </file>
@@ -3342,16 +3366,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FD60D78F-3821-4862-A3F3-4D76AD7CB293}" name="Table2" displayName="Table2" ref="A1:G358" totalsRowShown="0">
-  <autoFilter ref="A1:G358" xr:uid="{FD60D78F-3821-4862-A3F3-4D76AD7CB293}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{13438EE1-074A-4449-BE8D-27903006FAA3}" name="Table1" displayName="Table1" ref="A1:G360" totalsRowShown="0">
+  <autoFilter ref="A1:G360" xr:uid="{13438EE1-074A-4449-BE8D-27903006FAA3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G360">
+    <sortCondition ref="D1:D360"/>
+  </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{21652980-9163-45C4-A7C2-904E9A824535}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{E15EAF1C-FC0A-47B5-B4EC-1C6A4996EE94}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{70F9E0C3-450F-4860-B82E-CBA8D4D9A1CE}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{89674BC8-4897-4702-8C08-C63E44AA622F}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{A2A9D40F-8FC6-4AF3-A004-388470908D0C}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{A8976111-3615-4A06-B796-A00D3BD2A310}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{5D7EC063-DE01-4A33-BC90-3F6418A9E996}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{2F9065F2-5901-4F96-98D6-8F8C63743318}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{8427AFE0-4296-4814-BDE4-18D2AD1C6C59}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{A4B92CDF-E281-4DEC-B032-140BD4649077}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{65D72D06-6121-418E-A1EA-059D1306D2CE}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{6CEC7ED8-E162-447F-9445-138F9D8B822F}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{298D6095-4B35-4E60-BB89-612CEF7E32DA}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{40E984E7-66EC-475F-81E0-4AD05DD37944}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3619,8 +3646,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E442AD-E969-4DD3-924E-CD6AB4F546DE}">
-  <dimension ref="A1:G358"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C248886D-DFA2-4C46-938B-72AE3CDFD19E}">
+  <dimension ref="A1:G360"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -3660,13 +3687,13 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
@@ -3680,13 +3707,13 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>914</v>
+        <v>901</v>
       </c>
       <c r="D3" t="s">
-        <v>915</v>
+        <v>902</v>
       </c>
       <c r="E3" t="s">
-        <v>916</v>
+        <v>903</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
@@ -3700,13 +3727,13 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>912</v>
+        <v>899</v>
       </c>
       <c r="D4" t="s">
-        <v>913</v>
+        <v>900</v>
       </c>
       <c r="E4" t="s">
-        <v>911</v>
+        <v>898</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
@@ -3720,13 +3747,13 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="F5" t="s">
         <v>7</v>
@@ -3740,13 +3767,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
@@ -3760,13 +3787,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="F7" t="s">
         <v>7</v>
@@ -3780,13 +3807,13 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="F8" t="s">
         <v>7</v>
@@ -3800,13 +3827,13 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D9" t="s">
         <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="F9" t="s">
         <v>7</v>
@@ -3820,13 +3847,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="F10" t="s">
         <v>7</v>
@@ -3840,13 +3867,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>317</v>
+        <v>1063</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1064</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>1065</v>
       </c>
       <c r="E11" t="s">
-        <v>617</v>
+        <v>1066</v>
       </c>
       <c r="F11" t="s">
         <v>7</v>
@@ -3860,13 +3890,13 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>977</v>
+        <v>961</v>
       </c>
       <c r="D12" t="s">
-        <v>978</v>
+        <v>962</v>
       </c>
       <c r="E12" t="s">
-        <v>979</v>
+        <v>963</v>
       </c>
       <c r="F12" t="s">
         <v>7</v>
@@ -3880,16 +3910,16 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>980</v>
+        <v>964</v>
       </c>
       <c r="D13" t="s">
-        <v>981</v>
+        <v>965</v>
       </c>
       <c r="E13" t="s">
-        <v>982</v>
+        <v>966</v>
       </c>
       <c r="F13" t="s">
-        <v>910</v>
+        <v>897</v>
       </c>
       <c r="G13" t="s">
         <v>8</v>
@@ -3900,13 +3930,13 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
@@ -3920,13 +3950,13 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="F15" t="s">
         <v>7</v>
@@ -3940,13 +3970,13 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="F16" t="s">
         <v>7</v>
@@ -3960,13 +3990,13 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="F17" t="s">
         <v>7</v>
@@ -3980,13 +4010,13 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="F18" t="s">
         <v>7</v>
@@ -4000,13 +4030,13 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="F19" t="s">
         <v>7</v>
@@ -4020,13 +4050,13 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="F20" t="s">
         <v>7</v>
@@ -4040,13 +4070,13 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>325</v>
+        <v>1067</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>1068</v>
       </c>
       <c r="E21" t="s">
-        <v>625</v>
+        <v>1069</v>
       </c>
       <c r="F21" t="s">
         <v>7</v>
@@ -4060,13 +4090,13 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F22" t="s">
         <v>7</v>
@@ -4080,13 +4110,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E23" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F23" t="s">
         <v>7</v>
@@ -4100,13 +4130,13 @@
         <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E24" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F24" t="s">
         <v>7</v>
@@ -4120,13 +4150,13 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="D25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E25" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="F25" t="s">
         <v>7</v>
@@ -4140,13 +4170,13 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>917</v>
+        <v>324</v>
       </c>
       <c r="D26" t="s">
-        <v>918</v>
+        <v>28</v>
       </c>
       <c r="E26" t="s">
-        <v>919</v>
+        <v>619</v>
       </c>
       <c r="F26" t="s">
         <v>7</v>
@@ -4160,13 +4190,13 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>330</v>
+        <v>904</v>
       </c>
       <c r="D27" t="s">
-        <v>30</v>
+        <v>905</v>
       </c>
       <c r="E27" t="s">
-        <v>630</v>
+        <v>906</v>
       </c>
       <c r="F27" t="s">
         <v>7</v>
@@ -4180,13 +4210,13 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E28" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="F28" t="s">
         <v>7</v>
@@ -4200,13 +4230,13 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D29" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E29" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="F29" t="s">
         <v>7</v>
@@ -4220,13 +4250,13 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D30" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E30" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="F30" t="s">
         <v>7</v>
@@ -4240,13 +4270,13 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="D31" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E31" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="F31" t="s">
         <v>7</v>
@@ -4260,13 +4290,13 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="D32" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E32" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="F32" t="s">
         <v>7</v>
@@ -4280,16 +4310,16 @@
         <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="F33" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G33" t="s">
         <v>8</v>
@@ -4300,16 +4330,16 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E34" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="F34" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G34" t="s">
         <v>8</v>
@@ -4320,13 +4350,13 @@
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E35" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="F35" t="s">
         <v>7</v>
@@ -4340,13 +4370,13 @@
         <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="D36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E36" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="F36" t="s">
         <v>7</v>
@@ -4360,16 +4390,16 @@
         <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="D37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E37" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="F37" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G37" t="s">
         <v>8</v>
@@ -4380,16 +4410,16 @@
         <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D38" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E38" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="F38" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G38" t="s">
         <v>8</v>
@@ -4400,13 +4430,13 @@
         <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D39" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E39" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="F39" t="s">
         <v>7</v>
@@ -4420,13 +4450,13 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="D40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E40" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="F40" t="s">
         <v>7</v>
@@ -4440,13 +4470,13 @@
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>1008</v>
+        <v>990</v>
       </c>
       <c r="D41" t="s">
-        <v>1009</v>
+        <v>991</v>
       </c>
       <c r="E41" t="s">
-        <v>1010</v>
+        <v>992</v>
       </c>
       <c r="F41" t="s">
         <v>7</v>
@@ -4460,13 +4490,13 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D42" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E42" t="s">
-        <v>644</v>
+        <v>633</v>
       </c>
       <c r="F42" t="s">
         <v>7</v>
@@ -4480,13 +4510,13 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D43" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E43" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="F43" t="s">
         <v>7</v>
@@ -4500,16 +4530,16 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D44" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E44" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="F44" t="s">
-        <v>910</v>
+        <v>897</v>
       </c>
       <c r="G44" t="s">
         <v>8</v>
@@ -4520,16 +4550,16 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D45" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E45" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="F45" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G45" t="s">
         <v>8</v>
@@ -4540,13 +4570,13 @@
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D46" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E46" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="F46" t="s">
         <v>7</v>
@@ -4560,13 +4590,13 @@
         <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D47" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E47" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="F47" t="s">
         <v>7</v>
@@ -4580,13 +4610,13 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>350</v>
+        <v>910</v>
       </c>
       <c r="D48" t="s">
-        <v>50</v>
+        <v>911</v>
       </c>
       <c r="E48" t="s">
-        <v>650</v>
+        <v>912</v>
       </c>
       <c r="F48" t="s">
         <v>7</v>
@@ -4600,13 +4630,13 @@
         <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>923</v>
+        <v>344</v>
       </c>
       <c r="D49" t="s">
-        <v>924</v>
+        <v>48</v>
       </c>
       <c r="E49" t="s">
-        <v>925</v>
+        <v>639</v>
       </c>
       <c r="F49" t="s">
         <v>7</v>
@@ -4620,13 +4650,13 @@
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E50" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="F50" t="s">
         <v>7</v>
@@ -4640,13 +4670,13 @@
         <v>9</v>
       </c>
       <c r="B51" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D51" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E51" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="F51" t="s">
         <v>7</v>
@@ -4660,13 +4690,13 @@
         <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D52" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E52" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="F52" t="s">
         <v>7</v>
@@ -4680,13 +4710,13 @@
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D53" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E53" t="s">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="F53" t="s">
         <v>7</v>
@@ -4700,13 +4730,13 @@
         <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D54" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E54" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="F54" t="s">
         <v>7</v>
@@ -4720,16 +4750,16 @@
         <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D55" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E55" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="F55" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G55" t="s">
         <v>8</v>
@@ -4740,16 +4770,16 @@
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>357</v>
+        <v>993</v>
       </c>
       <c r="D56" t="s">
-        <v>57</v>
+        <v>994</v>
       </c>
       <c r="E56" t="s">
-        <v>657</v>
+        <v>995</v>
       </c>
       <c r="F56" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G56" t="s">
         <v>8</v>
@@ -4760,13 +4790,13 @@
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>1011</v>
+        <v>351</v>
       </c>
       <c r="D57" t="s">
-        <v>1012</v>
+        <v>55</v>
       </c>
       <c r="E57" t="s">
-        <v>1013</v>
+        <v>646</v>
       </c>
       <c r="F57" t="s">
         <v>7</v>
@@ -4780,13 +4810,13 @@
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D58" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E58" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="F58" t="s">
         <v>7</v>
@@ -4800,13 +4830,13 @@
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>359</v>
+        <v>939</v>
       </c>
       <c r="D59" t="s">
-        <v>59</v>
+        <v>940</v>
       </c>
       <c r="E59" t="s">
-        <v>659</v>
+        <v>941</v>
       </c>
       <c r="F59" t="s">
         <v>7</v>
@@ -4820,13 +4850,13 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>953</v>
+        <v>353</v>
       </c>
       <c r="D60" t="s">
-        <v>954</v>
+        <v>57</v>
       </c>
       <c r="E60" t="s">
-        <v>955</v>
+        <v>648</v>
       </c>
       <c r="F60" t="s">
         <v>7</v>
@@ -4840,16 +4870,16 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D61" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="F61" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G61" t="s">
         <v>8</v>
@@ -4860,16 +4890,16 @@
         <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="D62" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E62" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="F62" t="s">
-        <v>910</v>
+        <v>897</v>
       </c>
       <c r="G62" t="s">
         <v>8</v>
@@ -4880,16 +4910,16 @@
         <v>9</v>
       </c>
       <c r="B63" t="s">
-        <v>362</v>
+        <v>913</v>
       </c>
       <c r="D63" t="s">
-        <v>62</v>
+        <v>914</v>
       </c>
       <c r="E63" t="s">
-        <v>662</v>
+        <v>915</v>
       </c>
       <c r="F63" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G63" t="s">
         <v>8</v>
@@ -4900,13 +4930,13 @@
         <v>9</v>
       </c>
       <c r="B64" t="s">
-        <v>926</v>
+        <v>356</v>
       </c>
       <c r="D64" t="s">
-        <v>927</v>
+        <v>60</v>
       </c>
       <c r="E64" t="s">
-        <v>928</v>
+        <v>651</v>
       </c>
       <c r="F64" t="s">
         <v>7</v>
@@ -4920,13 +4950,13 @@
         <v>9</v>
       </c>
       <c r="B65" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="D65" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E65" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="F65" t="s">
         <v>7</v>
@@ -4940,13 +4970,13 @@
         <v>9</v>
       </c>
       <c r="B66" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D66" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E66" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="F66" t="s">
         <v>7</v>
@@ -4960,13 +4990,13 @@
         <v>9</v>
       </c>
       <c r="B67" t="s">
-        <v>365</v>
+        <v>1070</v>
       </c>
       <c r="D67" t="s">
-        <v>65</v>
+        <v>916</v>
       </c>
       <c r="E67" t="s">
-        <v>665</v>
+        <v>917</v>
       </c>
       <c r="F67" t="s">
         <v>7</v>
@@ -4980,13 +5010,13 @@
         <v>9</v>
       </c>
       <c r="B68" t="s">
-        <v>929</v>
+        <v>359</v>
       </c>
       <c r="D68" t="s">
-        <v>930</v>
+        <v>63</v>
       </c>
       <c r="E68" t="s">
-        <v>931</v>
+        <v>654</v>
       </c>
       <c r="F68" t="s">
         <v>7</v>
@@ -5000,13 +5030,13 @@
         <v>9</v>
       </c>
       <c r="B69" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="D69" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E69" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
       <c r="F69" t="s">
         <v>7</v>
@@ -5020,16 +5050,19 @@
         <v>9</v>
       </c>
       <c r="B70" t="s">
-        <v>367</v>
+        <v>996</v>
+      </c>
+      <c r="C70" t="s">
+        <v>997</v>
       </c>
       <c r="D70" t="s">
-        <v>67</v>
+        <v>998</v>
       </c>
       <c r="E70" t="s">
-        <v>667</v>
+        <v>999</v>
       </c>
       <c r="F70" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G70" t="s">
         <v>8</v>
@@ -5040,19 +5073,16 @@
         <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1015</v>
+        <v>361</v>
       </c>
       <c r="D71" t="s">
-        <v>1016</v>
+        <v>65</v>
       </c>
       <c r="E71" t="s">
-        <v>1017</v>
+        <v>656</v>
       </c>
       <c r="F71" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G71" t="s">
         <v>8</v>
@@ -5063,13 +5093,13 @@
         <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>368</v>
+        <v>907</v>
       </c>
       <c r="D72" t="s">
-        <v>68</v>
+        <v>908</v>
       </c>
       <c r="E72" t="s">
-        <v>668</v>
+        <v>909</v>
       </c>
       <c r="F72" t="s">
         <v>7</v>
@@ -5083,13 +5113,13 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>920</v>
+        <v>362</v>
       </c>
       <c r="D73" t="s">
-        <v>921</v>
+        <v>66</v>
       </c>
       <c r="E73" t="s">
-        <v>922</v>
+        <v>657</v>
       </c>
       <c r="F73" t="s">
         <v>7</v>
@@ -5103,13 +5133,13 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="D74" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E74" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="F74" t="s">
         <v>7</v>
@@ -5123,13 +5153,13 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D75" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E75" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="F75" t="s">
         <v>7</v>
@@ -5143,13 +5173,13 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="D76" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E76" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="F76" t="s">
         <v>7</v>
@@ -5163,13 +5193,13 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D77" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E77" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="F77" t="s">
         <v>7</v>
@@ -5183,13 +5213,13 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="D78" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E78" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="F78" t="s">
         <v>7</v>
@@ -5203,13 +5233,13 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="D79" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E79" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="F79" t="s">
         <v>7</v>
@@ -5223,13 +5253,13 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="D80" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E80" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="F80" t="s">
         <v>7</v>
@@ -5243,13 +5273,13 @@
         <v>9</v>
       </c>
       <c r="B81" t="s">
-        <v>376</v>
+        <v>1030</v>
       </c>
       <c r="D81" t="s">
-        <v>76</v>
+        <v>1031</v>
       </c>
       <c r="E81" t="s">
-        <v>676</v>
+        <v>1032</v>
       </c>
       <c r="F81" t="s">
         <v>7</v>
@@ -5263,13 +5293,13 @@
         <v>9</v>
       </c>
       <c r="B82" t="s">
-        <v>1054</v>
+        <v>370</v>
       </c>
       <c r="D82" t="s">
-        <v>1055</v>
+        <v>74</v>
       </c>
       <c r="E82" t="s">
-        <v>1056</v>
+        <v>665</v>
       </c>
       <c r="F82" t="s">
         <v>7</v>
@@ -5283,13 +5313,13 @@
         <v>9</v>
       </c>
       <c r="B83" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D83" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E83" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
       <c r="F83" t="s">
         <v>7</v>
@@ -5303,13 +5333,13 @@
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="D84" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E84" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="F84" t="s">
         <v>7</v>
@@ -5323,13 +5353,13 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="D85" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E85" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="F85" t="s">
         <v>7</v>
@@ -5343,13 +5373,13 @@
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="D86" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E86" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="F86" t="s">
         <v>7</v>
@@ -5363,16 +5393,16 @@
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="D87" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E87" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="F87" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G87" t="s">
         <v>8</v>
@@ -5383,16 +5413,16 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D88" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E88" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="F88" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G88" t="s">
         <v>8</v>
@@ -5403,13 +5433,13 @@
         <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="D89" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E89" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="F89" t="s">
         <v>7</v>
@@ -5423,13 +5453,13 @@
         <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="D90" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E90" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
       <c r="F90" t="s">
         <v>7</v>
@@ -5443,13 +5473,13 @@
         <v>9</v>
       </c>
       <c r="B91" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="D91" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E91" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="F91" t="s">
         <v>7</v>
@@ -5463,13 +5493,13 @@
         <v>9</v>
       </c>
       <c r="B92" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="D92" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E92" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="F92" t="s">
         <v>7</v>
@@ -5483,13 +5513,13 @@
         <v>9</v>
       </c>
       <c r="B93" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="D93" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E93" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
       <c r="F93" t="s">
         <v>7</v>
@@ -5503,13 +5533,13 @@
         <v>9</v>
       </c>
       <c r="B94" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="D94" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E94" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="F94" t="s">
         <v>7</v>
@@ -5523,13 +5553,13 @@
         <v>9</v>
       </c>
       <c r="B95" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="D95" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E95" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="F95" t="s">
         <v>7</v>
@@ -5543,13 +5573,13 @@
         <v>9</v>
       </c>
       <c r="B96" t="s">
-        <v>390</v>
+        <v>918</v>
       </c>
       <c r="D96" t="s">
-        <v>90</v>
+        <v>919</v>
       </c>
       <c r="E96" t="s">
-        <v>690</v>
+        <v>920</v>
       </c>
       <c r="F96" t="s">
         <v>7</v>
@@ -5563,13 +5593,13 @@
         <v>9</v>
       </c>
       <c r="B97" t="s">
-        <v>932</v>
+        <v>384</v>
       </c>
       <c r="D97" t="s">
-        <v>933</v>
+        <v>88</v>
       </c>
       <c r="E97" t="s">
-        <v>934</v>
+        <v>679</v>
       </c>
       <c r="F97" t="s">
         <v>7</v>
@@ -5583,13 +5613,13 @@
         <v>9</v>
       </c>
       <c r="B98" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="D98" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E98" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
       <c r="F98" t="s">
         <v>7</v>
@@ -5603,13 +5633,13 @@
         <v>9</v>
       </c>
       <c r="B99" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D99" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E99" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="F99" t="s">
         <v>7</v>
@@ -5623,13 +5653,13 @@
         <v>9</v>
       </c>
       <c r="B100" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="D100" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E100" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="F100" t="s">
         <v>7</v>
@@ -5643,13 +5673,13 @@
         <v>9</v>
       </c>
       <c r="B101" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="D101" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E101" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="F101" t="s">
         <v>7</v>
@@ -5663,13 +5693,13 @@
         <v>9</v>
       </c>
       <c r="B102" t="s">
-        <v>395</v>
+        <v>921</v>
       </c>
       <c r="D102" t="s">
-        <v>95</v>
+        <v>922</v>
       </c>
       <c r="E102" t="s">
-        <v>695</v>
+        <v>923</v>
       </c>
       <c r="F102" t="s">
         <v>7</v>
@@ -5683,13 +5713,13 @@
         <v>9</v>
       </c>
       <c r="B103" t="s">
-        <v>935</v>
+        <v>389</v>
       </c>
       <c r="D103" t="s">
-        <v>936</v>
+        <v>93</v>
       </c>
       <c r="E103" t="s">
-        <v>937</v>
+        <v>684</v>
       </c>
       <c r="F103" t="s">
         <v>7</v>
@@ -5703,13 +5733,13 @@
         <v>9</v>
       </c>
       <c r="B104" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D104" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E104" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="F104" t="s">
         <v>7</v>
@@ -5723,13 +5753,13 @@
         <v>9</v>
       </c>
       <c r="B105" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D105" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E105" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="F105" t="s">
         <v>7</v>
@@ -5743,13 +5773,13 @@
         <v>9</v>
       </c>
       <c r="B106" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D106" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E106" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="F106" t="s">
         <v>7</v>
@@ -5763,13 +5793,13 @@
         <v>9</v>
       </c>
       <c r="B107" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="D107" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E107" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="F107" t="s">
         <v>7</v>
@@ -5783,13 +5813,13 @@
         <v>9</v>
       </c>
       <c r="B108" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D108" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E108" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="F108" t="s">
         <v>7</v>
@@ -5803,13 +5833,13 @@
         <v>9</v>
       </c>
       <c r="B109" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="D109" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E109" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="F109" t="s">
         <v>7</v>
@@ -5823,13 +5853,13 @@
         <v>9</v>
       </c>
       <c r="B110" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="D110" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E110" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="F110" t="s">
         <v>7</v>
@@ -5843,16 +5873,16 @@
         <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>403</v>
+        <v>1033</v>
       </c>
       <c r="D111" t="s">
-        <v>103</v>
+        <v>1034</v>
       </c>
       <c r="E111" t="s">
-        <v>703</v>
+        <v>1035</v>
       </c>
       <c r="F111" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G111" t="s">
         <v>8</v>
@@ -5863,16 +5893,16 @@
         <v>9</v>
       </c>
       <c r="B112" t="s">
-        <v>1057</v>
+        <v>397</v>
       </c>
       <c r="D112" t="s">
-        <v>1058</v>
+        <v>101</v>
       </c>
       <c r="E112" t="s">
-        <v>1059</v>
+        <v>692</v>
       </c>
       <c r="F112" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G112" t="s">
         <v>8</v>
@@ -5883,13 +5913,13 @@
         <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>404</v>
+        <v>980</v>
       </c>
       <c r="D113" t="s">
-        <v>104</v>
+        <v>981</v>
       </c>
       <c r="E113" t="s">
-        <v>704</v>
+        <v>982</v>
       </c>
       <c r="F113" t="s">
         <v>7</v>
@@ -5903,13 +5933,13 @@
         <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>998</v>
+        <v>398</v>
       </c>
       <c r="D114" t="s">
-        <v>999</v>
+        <v>102</v>
       </c>
       <c r="E114" t="s">
-        <v>1000</v>
+        <v>693</v>
       </c>
       <c r="F114" t="s">
         <v>7</v>
@@ -5923,13 +5953,13 @@
         <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D115" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E115" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="F115" t="s">
         <v>7</v>
@@ -5943,13 +5973,13 @@
         <v>9</v>
       </c>
       <c r="B116" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="D116" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E116" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="F116" t="s">
         <v>7</v>
@@ -5963,13 +5993,13 @@
         <v>9</v>
       </c>
       <c r="B117" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="D117" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E117" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="F117" t="s">
         <v>7</v>
@@ -5983,13 +6013,13 @@
         <v>9</v>
       </c>
       <c r="B118" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="D118" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E118" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="F118" t="s">
         <v>7</v>
@@ -6003,13 +6033,13 @@
         <v>9</v>
       </c>
       <c r="B119" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D119" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E119" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="F119" t="s">
         <v>7</v>
@@ -6023,13 +6053,13 @@
         <v>9</v>
       </c>
       <c r="B120" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D120" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E120" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="F120" t="s">
         <v>7</v>
@@ -6043,16 +6073,16 @@
         <v>9</v>
       </c>
       <c r="B121" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D121" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E121" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="F121" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G121" t="s">
         <v>8</v>
@@ -6063,16 +6093,16 @@
         <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="D122" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E122" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="F122" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G122" t="s">
         <v>8</v>
@@ -6083,13 +6113,13 @@
         <v>9</v>
       </c>
       <c r="B123" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D123" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E123" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="F123" t="s">
         <v>7</v>
@@ -6103,16 +6133,16 @@
         <v>9</v>
       </c>
       <c r="B124" t="s">
-        <v>414</v>
+        <v>930</v>
       </c>
       <c r="D124" t="s">
-        <v>114</v>
+        <v>931</v>
       </c>
       <c r="E124" t="s">
-        <v>714</v>
+        <v>932</v>
       </c>
       <c r="F124" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G124" t="s">
         <v>8</v>
@@ -6123,16 +6153,16 @@
         <v>9</v>
       </c>
       <c r="B125" t="s">
-        <v>944</v>
+        <v>933</v>
       </c>
       <c r="D125" t="s">
-        <v>945</v>
+        <v>934</v>
       </c>
       <c r="E125" t="s">
-        <v>946</v>
+        <v>935</v>
       </c>
       <c r="F125" t="s">
-        <v>910</v>
+        <v>897</v>
       </c>
       <c r="G125" t="s">
         <v>8</v>
@@ -6143,16 +6173,16 @@
         <v>9</v>
       </c>
       <c r="B126" t="s">
-        <v>947</v>
+        <v>408</v>
       </c>
       <c r="D126" t="s">
-        <v>948</v>
+        <v>112</v>
       </c>
       <c r="E126" t="s">
-        <v>949</v>
+        <v>703</v>
       </c>
       <c r="F126" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G126" t="s">
         <v>8</v>
@@ -6163,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B127" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D127" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E127" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="F127" t="s">
         <v>7</v>
@@ -6183,16 +6213,16 @@
         <v>9</v>
       </c>
       <c r="B128" t="s">
-        <v>416</v>
+        <v>1071</v>
       </c>
       <c r="D128" t="s">
-        <v>116</v>
+        <v>1036</v>
       </c>
       <c r="E128" t="s">
-        <v>716</v>
+        <v>1037</v>
       </c>
       <c r="F128" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G128" t="s">
         <v>8</v>
@@ -6203,16 +6233,16 @@
         <v>9</v>
       </c>
       <c r="B129" t="s">
-        <v>1060</v>
+        <v>410</v>
       </c>
       <c r="D129" t="s">
-        <v>1061</v>
+        <v>114</v>
       </c>
       <c r="E129" t="s">
-        <v>1062</v>
+        <v>705</v>
       </c>
       <c r="F129" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G129" t="s">
         <v>8</v>
@@ -6223,13 +6253,13 @@
         <v>9</v>
       </c>
       <c r="B130" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D130" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E130" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="F130" t="s">
         <v>7</v>
@@ -6243,13 +6273,13 @@
         <v>9</v>
       </c>
       <c r="B131" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D131" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E131" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="F131" t="s">
         <v>7</v>
@@ -6263,16 +6293,16 @@
         <v>9</v>
       </c>
       <c r="B132" t="s">
-        <v>419</v>
+        <v>1000</v>
       </c>
       <c r="D132" t="s">
-        <v>119</v>
+        <v>1001</v>
       </c>
       <c r="E132" t="s">
-        <v>719</v>
+        <v>1002</v>
       </c>
       <c r="F132" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G132" t="s">
         <v>8</v>
@@ -6283,16 +6313,16 @@
         <v>9</v>
       </c>
       <c r="B133" t="s">
-        <v>1018</v>
+        <v>413</v>
       </c>
       <c r="D133" t="s">
-        <v>1019</v>
+        <v>117</v>
       </c>
       <c r="E133" t="s">
-        <v>1020</v>
+        <v>708</v>
       </c>
       <c r="F133" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G133" t="s">
         <v>8</v>
@@ -6303,13 +6333,13 @@
         <v>9</v>
       </c>
       <c r="B134" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D134" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E134" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="F134" t="s">
         <v>7</v>
@@ -6323,13 +6353,13 @@
         <v>9</v>
       </c>
       <c r="B135" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="D135" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E135" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="F135" t="s">
         <v>7</v>
@@ -6343,13 +6373,13 @@
         <v>9</v>
       </c>
       <c r="B136" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D136" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E136" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="F136" t="s">
         <v>7</v>
@@ -6363,13 +6393,13 @@
         <v>9</v>
       </c>
       <c r="B137" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D137" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E137" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="F137" t="s">
         <v>7</v>
@@ -6383,13 +6413,13 @@
         <v>9</v>
       </c>
       <c r="B138" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D138" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E138" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="F138" t="s">
         <v>7</v>
@@ -6403,16 +6433,16 @@
         <v>9</v>
       </c>
       <c r="B139" t="s">
-        <v>425</v>
+        <v>1072</v>
       </c>
       <c r="D139" t="s">
-        <v>125</v>
+        <v>1073</v>
       </c>
       <c r="E139" t="s">
-        <v>725</v>
+        <v>1074</v>
       </c>
       <c r="F139" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G139" t="s">
         <v>8</v>
@@ -6423,13 +6453,13 @@
         <v>9</v>
       </c>
       <c r="B140" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="D140" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E140" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="F140" t="s">
         <v>7</v>
@@ -6443,13 +6473,13 @@
         <v>9</v>
       </c>
       <c r="B141" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="D141" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E141" t="s">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="F141" t="s">
         <v>7</v>
@@ -6463,13 +6493,13 @@
         <v>9</v>
       </c>
       <c r="B142" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="D142" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E142" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="F142" t="s">
         <v>7</v>
@@ -6483,13 +6513,13 @@
         <v>9</v>
       </c>
       <c r="B143" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="D143" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E143" t="s">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="F143" t="s">
         <v>7</v>
@@ -6503,16 +6533,16 @@
         <v>9</v>
       </c>
       <c r="B144" t="s">
-        <v>1063</v>
+        <v>1038</v>
       </c>
       <c r="C144" t="s">
-        <v>1064</v>
+        <v>1039</v>
       </c>
       <c r="D144" t="s">
-        <v>1065</v>
+        <v>1040</v>
       </c>
       <c r="E144" t="s">
-        <v>1066</v>
+        <v>1041</v>
       </c>
       <c r="F144" t="s">
         <v>7</v>
@@ -6526,13 +6556,13 @@
         <v>9</v>
       </c>
       <c r="B145" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="D145" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E145" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="F145" t="s">
         <v>7</v>
@@ -6546,13 +6576,16 @@
         <v>9</v>
       </c>
       <c r="B146" t="s">
-        <v>938</v>
+        <v>1075</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1076</v>
       </c>
       <c r="D146" t="s">
-        <v>939</v>
+        <v>1077</v>
       </c>
       <c r="E146" t="s">
-        <v>940</v>
+        <v>1078</v>
       </c>
       <c r="F146" t="s">
         <v>7</v>
@@ -6566,13 +6599,13 @@
         <v>9</v>
       </c>
       <c r="B147" t="s">
-        <v>431</v>
+        <v>924</v>
       </c>
       <c r="D147" t="s">
-        <v>131</v>
+        <v>925</v>
       </c>
       <c r="E147" t="s">
-        <v>731</v>
+        <v>926</v>
       </c>
       <c r="F147" t="s">
         <v>7</v>
@@ -6586,16 +6619,16 @@
         <v>9</v>
       </c>
       <c r="B148" t="s">
-        <v>941</v>
+        <v>424</v>
       </c>
       <c r="D148" t="s">
-        <v>942</v>
+        <v>128</v>
       </c>
       <c r="E148" t="s">
-        <v>943</v>
+        <v>719</v>
       </c>
       <c r="F148" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G148" t="s">
         <v>8</v>
@@ -6606,16 +6639,16 @@
         <v>9</v>
       </c>
       <c r="B149" t="s">
-        <v>432</v>
+        <v>927</v>
       </c>
       <c r="D149" t="s">
-        <v>132</v>
+        <v>928</v>
       </c>
       <c r="E149" t="s">
-        <v>732</v>
+        <v>929</v>
       </c>
       <c r="F149" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G149" t="s">
         <v>8</v>
@@ -6626,13 +6659,13 @@
         <v>9</v>
       </c>
       <c r="B150" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="D150" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E150" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="F150" t="s">
         <v>7</v>
@@ -6646,13 +6679,13 @@
         <v>9</v>
       </c>
       <c r="B151" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="D151" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E151" t="s">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="F151" t="s">
         <v>7</v>
@@ -6666,13 +6699,13 @@
         <v>9</v>
       </c>
       <c r="B152" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="D152" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E152" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="F152" t="s">
         <v>7</v>
@@ -6686,13 +6719,13 @@
         <v>9</v>
       </c>
       <c r="B153" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="D153" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E153" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="F153" t="s">
         <v>7</v>
@@ -6706,13 +6739,13 @@
         <v>9</v>
       </c>
       <c r="B154" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="D154" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E154" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="F154" t="s">
         <v>7</v>
@@ -6726,13 +6759,13 @@
         <v>9</v>
       </c>
       <c r="B155" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="D155" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E155" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="F155" t="s">
         <v>7</v>
@@ -6746,13 +6779,13 @@
         <v>9</v>
       </c>
       <c r="B156" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="D156" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E156" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="F156" t="s">
         <v>7</v>
@@ -6766,13 +6799,13 @@
         <v>9</v>
       </c>
       <c r="B157" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="D157" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E157" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="F157" t="s">
         <v>7</v>
@@ -6786,13 +6819,13 @@
         <v>9</v>
       </c>
       <c r="B158" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D158" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E158" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="F158" t="s">
         <v>7</v>
@@ -6806,13 +6839,13 @@
         <v>9</v>
       </c>
       <c r="B159" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="D159" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E159" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="F159" t="s">
         <v>7</v>
@@ -6826,13 +6859,13 @@
         <v>9</v>
       </c>
       <c r="B160" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="D160" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E160" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="F160" t="s">
         <v>7</v>
@@ -6846,13 +6879,13 @@
         <v>9</v>
       </c>
       <c r="B161" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="D161" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E161" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="F161" t="s">
         <v>7</v>
@@ -6866,13 +6899,13 @@
         <v>9</v>
       </c>
       <c r="B162" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D162" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E162" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="F162" t="s">
         <v>7</v>
@@ -6886,13 +6919,13 @@
         <v>9</v>
       </c>
       <c r="B163" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="D163" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E163" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="F163" t="s">
         <v>7</v>
@@ -6906,13 +6939,13 @@
         <v>9</v>
       </c>
       <c r="B164" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="D164" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E164" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="F164" t="s">
         <v>7</v>
@@ -6926,13 +6959,13 @@
         <v>9</v>
       </c>
       <c r="B165" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="D165" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E165" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="F165" t="s">
         <v>7</v>
@@ -6946,13 +6979,13 @@
         <v>9</v>
       </c>
       <c r="B166" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="D166" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E166" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="F166" t="s">
         <v>7</v>
@@ -6966,13 +6999,13 @@
         <v>9</v>
       </c>
       <c r="B167" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="D167" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E167" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="F167" t="s">
         <v>7</v>
@@ -6986,13 +7019,13 @@
         <v>9</v>
       </c>
       <c r="B168" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="D168" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E168" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="F168" t="s">
         <v>7</v>
@@ -7006,13 +7039,13 @@
         <v>9</v>
       </c>
       <c r="B169" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="D169" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E169" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="F169" t="s">
         <v>7</v>
@@ -7026,13 +7059,13 @@
         <v>9</v>
       </c>
       <c r="B170" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="D170" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E170" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
       <c r="F170" t="s">
         <v>7</v>
@@ -7046,16 +7079,16 @@
         <v>9</v>
       </c>
       <c r="B171" t="s">
-        <v>1021</v>
+        <v>446</v>
       </c>
       <c r="D171" t="s">
-        <v>1022</v>
+        <v>150</v>
       </c>
       <c r="E171" t="s">
-        <v>1023</v>
+        <v>741</v>
       </c>
       <c r="F171" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G171" t="s">
         <v>8</v>
@@ -7066,13 +7099,13 @@
         <v>9</v>
       </c>
       <c r="B172" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="D172" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E172" t="s">
-        <v>754</v>
+        <v>742</v>
       </c>
       <c r="F172" t="s">
         <v>7</v>
@@ -7086,13 +7119,13 @@
         <v>9</v>
       </c>
       <c r="B173" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="D173" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E173" t="s">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="F173" t="s">
         <v>7</v>
@@ -7106,13 +7139,13 @@
         <v>9</v>
       </c>
       <c r="B174" t="s">
-        <v>456</v>
+        <v>1079</v>
       </c>
       <c r="D174" t="s">
-        <v>156</v>
+        <v>1080</v>
       </c>
       <c r="E174" t="s">
-        <v>756</v>
+        <v>1081</v>
       </c>
       <c r="F174" t="s">
         <v>7</v>
@@ -7126,13 +7159,13 @@
         <v>9</v>
       </c>
       <c r="B175" t="s">
-        <v>1067</v>
+        <v>449</v>
       </c>
       <c r="D175" t="s">
-        <v>1068</v>
+        <v>153</v>
       </c>
       <c r="E175" t="s">
-        <v>1069</v>
+        <v>744</v>
       </c>
       <c r="F175" t="s">
         <v>7</v>
@@ -7146,13 +7179,13 @@
         <v>9</v>
       </c>
       <c r="B176" t="s">
-        <v>457</v>
+        <v>1042</v>
       </c>
       <c r="D176" t="s">
-        <v>157</v>
+        <v>1043</v>
       </c>
       <c r="E176" t="s">
-        <v>757</v>
+        <v>1044</v>
       </c>
       <c r="F176" t="s">
         <v>7</v>
@@ -7166,13 +7199,13 @@
         <v>9</v>
       </c>
       <c r="B177" t="s">
-        <v>950</v>
+        <v>450</v>
       </c>
       <c r="D177" t="s">
-        <v>951</v>
+        <v>154</v>
       </c>
       <c r="E177" t="s">
-        <v>952</v>
+        <v>745</v>
       </c>
       <c r="F177" t="s">
         <v>7</v>
@@ -7186,13 +7219,13 @@
         <v>9</v>
       </c>
       <c r="B178" t="s">
-        <v>956</v>
+        <v>936</v>
       </c>
       <c r="D178" t="s">
-        <v>957</v>
+        <v>937</v>
       </c>
       <c r="E178" t="s">
-        <v>958</v>
+        <v>938</v>
       </c>
       <c r="F178" t="s">
         <v>7</v>
@@ -7206,13 +7239,13 @@
         <v>9</v>
       </c>
       <c r="B179" t="s">
-        <v>458</v>
+        <v>942</v>
       </c>
       <c r="D179" t="s">
-        <v>158</v>
+        <v>943</v>
       </c>
       <c r="E179" t="s">
-        <v>758</v>
+        <v>944</v>
       </c>
       <c r="F179" t="s">
         <v>7</v>
@@ -7226,16 +7259,16 @@
         <v>9</v>
       </c>
       <c r="B180" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="D180" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E180" t="s">
-        <v>759</v>
+        <v>746</v>
       </c>
       <c r="F180" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G180" t="s">
         <v>8</v>
@@ -7246,16 +7279,16 @@
         <v>9</v>
       </c>
       <c r="B181" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="D181" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E181" t="s">
-        <v>760</v>
+        <v>747</v>
       </c>
       <c r="F181" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G181" t="s">
         <v>8</v>
@@ -7266,13 +7299,13 @@
         <v>9</v>
       </c>
       <c r="B182" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="D182" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E182" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
       <c r="F182" t="s">
         <v>7</v>
@@ -7286,13 +7319,13 @@
         <v>9</v>
       </c>
       <c r="B183" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="D183" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E183" t="s">
-        <v>762</v>
+        <v>749</v>
       </c>
       <c r="F183" t="s">
         <v>7</v>
@@ -7306,13 +7339,13 @@
         <v>9</v>
       </c>
       <c r="B184" t="s">
-        <v>959</v>
+        <v>455</v>
       </c>
       <c r="D184" t="s">
-        <v>960</v>
+        <v>159</v>
       </c>
       <c r="E184" t="s">
-        <v>961</v>
+        <v>750</v>
       </c>
       <c r="F184" t="s">
         <v>7</v>
@@ -7326,13 +7359,13 @@
         <v>9</v>
       </c>
       <c r="B185" t="s">
-        <v>463</v>
+        <v>945</v>
       </c>
       <c r="D185" t="s">
-        <v>163</v>
+        <v>946</v>
       </c>
       <c r="E185" t="s">
-        <v>763</v>
+        <v>947</v>
       </c>
       <c r="F185" t="s">
         <v>7</v>
@@ -7346,13 +7379,13 @@
         <v>9</v>
       </c>
       <c r="B186" t="s">
-        <v>962</v>
+        <v>456</v>
       </c>
       <c r="D186" t="s">
-        <v>963</v>
+        <v>160</v>
       </c>
       <c r="E186" t="s">
-        <v>964</v>
+        <v>751</v>
       </c>
       <c r="F186" t="s">
         <v>7</v>
@@ -7366,16 +7399,16 @@
         <v>9</v>
       </c>
       <c r="B187" t="s">
-        <v>464</v>
+        <v>1082</v>
       </c>
       <c r="D187" t="s">
-        <v>164</v>
+        <v>948</v>
       </c>
       <c r="E187" t="s">
-        <v>764</v>
+        <v>949</v>
       </c>
       <c r="F187" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G187" t="s">
         <v>8</v>
@@ -7386,16 +7419,16 @@
         <v>9</v>
       </c>
       <c r="B188" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="D188" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E188" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="F188" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G188" t="s">
         <v>8</v>
@@ -7406,13 +7439,13 @@
         <v>9</v>
       </c>
       <c r="B189" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D189" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E189" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
       <c r="F189" t="s">
         <v>7</v>
@@ -7426,13 +7459,13 @@
         <v>9</v>
       </c>
       <c r="B190" t="s">
-        <v>965</v>
+        <v>459</v>
       </c>
       <c r="D190" t="s">
-        <v>966</v>
+        <v>163</v>
       </c>
       <c r="E190" t="s">
-        <v>967</v>
+        <v>754</v>
       </c>
       <c r="F190" t="s">
         <v>7</v>
@@ -7446,13 +7479,13 @@
         <v>9</v>
       </c>
       <c r="B191" t="s">
-        <v>467</v>
+        <v>950</v>
       </c>
       <c r="D191" t="s">
-        <v>167</v>
+        <v>951</v>
       </c>
       <c r="E191" t="s">
-        <v>767</v>
+        <v>952</v>
       </c>
       <c r="F191" t="s">
         <v>7</v>
@@ -7466,13 +7499,13 @@
         <v>9</v>
       </c>
       <c r="B192" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="D192" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E192" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="F192" t="s">
         <v>7</v>
@@ -7486,13 +7519,13 @@
         <v>9</v>
       </c>
       <c r="B193" t="s">
-        <v>1024</v>
+        <v>461</v>
       </c>
       <c r="D193" t="s">
-        <v>1025</v>
+        <v>165</v>
       </c>
       <c r="E193" t="s">
-        <v>1026</v>
+        <v>756</v>
       </c>
       <c r="F193" t="s">
         <v>7</v>
@@ -7506,13 +7539,13 @@
         <v>9</v>
       </c>
       <c r="B194" t="s">
-        <v>469</v>
+        <v>1003</v>
       </c>
       <c r="D194" t="s">
-        <v>169</v>
+        <v>1004</v>
       </c>
       <c r="E194" t="s">
-        <v>769</v>
+        <v>1005</v>
       </c>
       <c r="F194" t="s">
         <v>7</v>
@@ -7526,16 +7559,16 @@
         <v>9</v>
       </c>
       <c r="B195" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="D195" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E195" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="F195" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G195" t="s">
         <v>8</v>
@@ -7546,16 +7579,16 @@
         <v>9</v>
       </c>
       <c r="B196" t="s">
-        <v>1070</v>
+        <v>463</v>
       </c>
       <c r="D196" t="s">
-        <v>1071</v>
+        <v>167</v>
       </c>
       <c r="E196" t="s">
-        <v>1072</v>
+        <v>758</v>
       </c>
       <c r="F196" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G196" t="s">
         <v>8</v>
@@ -7566,13 +7599,13 @@
         <v>9</v>
       </c>
       <c r="B197" t="s">
-        <v>1027</v>
+        <v>1083</v>
       </c>
       <c r="D197" t="s">
-        <v>1028</v>
+        <v>1045</v>
       </c>
       <c r="E197" t="s">
-        <v>1029</v>
+        <v>1046</v>
       </c>
       <c r="F197" t="s">
         <v>7</v>
@@ -7586,13 +7619,13 @@
         <v>9</v>
       </c>
       <c r="B198" t="s">
-        <v>471</v>
+        <v>1006</v>
       </c>
       <c r="D198" t="s">
-        <v>171</v>
+        <v>1007</v>
       </c>
       <c r="E198" t="s">
-        <v>771</v>
+        <v>1008</v>
       </c>
       <c r="F198" t="s">
         <v>7</v>
@@ -7606,13 +7639,13 @@
         <v>9</v>
       </c>
       <c r="B199" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="D199" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E199" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="F199" t="s">
         <v>7</v>
@@ -7626,16 +7659,16 @@
         <v>9</v>
       </c>
       <c r="B200" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="D200" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E200" t="s">
-        <v>773</v>
+        <v>760</v>
       </c>
       <c r="F200" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G200" t="s">
         <v>8</v>
@@ -7646,16 +7679,16 @@
         <v>9</v>
       </c>
       <c r="B201" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="D201" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E201" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="F201" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G201" t="s">
         <v>8</v>
@@ -7666,13 +7699,13 @@
         <v>9</v>
       </c>
       <c r="B202" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="D202" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E202" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
       <c r="F202" t="s">
         <v>7</v>
@@ -7686,16 +7719,16 @@
         <v>9</v>
       </c>
       <c r="B203" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="D203" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E203" t="s">
-        <v>776</v>
+        <v>763</v>
       </c>
       <c r="F203" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G203" t="s">
         <v>8</v>
@@ -7706,16 +7739,16 @@
         <v>9</v>
       </c>
       <c r="B204" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="D204" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E204" t="s">
-        <v>777</v>
+        <v>764</v>
       </c>
       <c r="F204" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G204" t="s">
         <v>8</v>
@@ -7726,13 +7759,13 @@
         <v>9</v>
       </c>
       <c r="B205" t="s">
-        <v>971</v>
+        <v>470</v>
       </c>
       <c r="D205" t="s">
-        <v>972</v>
+        <v>174</v>
       </c>
       <c r="E205" t="s">
-        <v>973</v>
+        <v>765</v>
       </c>
       <c r="F205" t="s">
         <v>7</v>
@@ -7746,13 +7779,13 @@
         <v>9</v>
       </c>
       <c r="B206" t="s">
-        <v>478</v>
+        <v>956</v>
       </c>
       <c r="D206" t="s">
-        <v>178</v>
+        <v>957</v>
       </c>
       <c r="E206" t="s">
-        <v>778</v>
+        <v>958</v>
       </c>
       <c r="F206" t="s">
         <v>7</v>
@@ -7766,13 +7799,13 @@
         <v>9</v>
       </c>
       <c r="B207" t="s">
-        <v>968</v>
+        <v>471</v>
       </c>
       <c r="D207" t="s">
-        <v>969</v>
+        <v>175</v>
       </c>
       <c r="E207" t="s">
-        <v>970</v>
+        <v>766</v>
       </c>
       <c r="F207" t="s">
         <v>7</v>
@@ -7786,13 +7819,13 @@
         <v>9</v>
       </c>
       <c r="B208" t="s">
-        <v>479</v>
+        <v>953</v>
       </c>
       <c r="D208" t="s">
-        <v>179</v>
+        <v>954</v>
       </c>
       <c r="E208" t="s">
-        <v>779</v>
+        <v>955</v>
       </c>
       <c r="F208" t="s">
         <v>7</v>
@@ -7806,13 +7839,13 @@
         <v>9</v>
       </c>
       <c r="B209" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="D209" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E209" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="F209" t="s">
         <v>7</v>
@@ -7826,13 +7859,13 @@
         <v>9</v>
       </c>
       <c r="B210" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="D210" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E210" t="s">
-        <v>781</v>
+        <v>768</v>
       </c>
       <c r="F210" t="s">
         <v>7</v>
@@ -7846,13 +7879,13 @@
         <v>9</v>
       </c>
       <c r="B211" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="D211" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E211" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="F211" t="s">
         <v>7</v>
@@ -7866,13 +7899,13 @@
         <v>9</v>
       </c>
       <c r="B212" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="D212" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E212" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="F212" t="s">
         <v>7</v>
@@ -7886,13 +7919,13 @@
         <v>9</v>
       </c>
       <c r="B213" t="s">
-        <v>974</v>
+        <v>476</v>
       </c>
       <c r="D213" t="s">
-        <v>975</v>
+        <v>180</v>
       </c>
       <c r="E213" t="s">
-        <v>976</v>
+        <v>771</v>
       </c>
       <c r="F213" t="s">
         <v>7</v>
@@ -7906,13 +7939,13 @@
         <v>9</v>
       </c>
       <c r="B214" t="s">
-        <v>484</v>
+        <v>1084</v>
       </c>
       <c r="D214" t="s">
-        <v>184</v>
+        <v>959</v>
       </c>
       <c r="E214" t="s">
-        <v>784</v>
+        <v>960</v>
       </c>
       <c r="F214" t="s">
         <v>7</v>
@@ -7926,13 +7959,13 @@
         <v>9</v>
       </c>
       <c r="B215" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="D215" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E215" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
       <c r="F215" t="s">
         <v>7</v>
@@ -7946,13 +7979,13 @@
         <v>9</v>
       </c>
       <c r="B216" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="D216" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E216" t="s">
-        <v>786</v>
+        <v>773</v>
       </c>
       <c r="F216" t="s">
         <v>7</v>
@@ -7966,16 +7999,16 @@
         <v>9</v>
       </c>
       <c r="B217" t="s">
-        <v>1030</v>
+        <v>479</v>
       </c>
       <c r="D217" t="s">
-        <v>1031</v>
+        <v>183</v>
       </c>
       <c r="E217" t="s">
-        <v>1032</v>
+        <v>774</v>
       </c>
       <c r="F217" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G217" t="s">
         <v>8</v>
@@ -7986,16 +8019,16 @@
         <v>9</v>
       </c>
       <c r="B218" t="s">
-        <v>487</v>
+        <v>1009</v>
       </c>
       <c r="D218" t="s">
-        <v>187</v>
+        <v>1010</v>
       </c>
       <c r="E218" t="s">
-        <v>787</v>
+        <v>1011</v>
       </c>
       <c r="F218" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G218" t="s">
         <v>8</v>
@@ -8006,13 +8039,13 @@
         <v>9</v>
       </c>
       <c r="B219" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="D219" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E219" t="s">
-        <v>788</v>
+        <v>775</v>
       </c>
       <c r="F219" t="s">
         <v>7</v>
@@ -8026,13 +8059,13 @@
         <v>9</v>
       </c>
       <c r="B220" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="D220" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E220" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
       <c r="F220" t="s">
         <v>7</v>
@@ -8046,13 +8079,13 @@
         <v>9</v>
       </c>
       <c r="B221" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="D221" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E221" t="s">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="F221" t="s">
         <v>7</v>
@@ -8066,13 +8099,13 @@
         <v>9</v>
       </c>
       <c r="B222" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="D222" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E222" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
       <c r="F222" t="s">
         <v>7</v>
@@ -8086,13 +8119,13 @@
         <v>9</v>
       </c>
       <c r="B223" t="s">
-        <v>986</v>
+        <v>484</v>
       </c>
       <c r="D223" t="s">
-        <v>987</v>
+        <v>188</v>
       </c>
       <c r="E223" t="s">
-        <v>988</v>
+        <v>779</v>
       </c>
       <c r="F223" t="s">
         <v>7</v>
@@ -8106,16 +8139,13 @@
         <v>9</v>
       </c>
       <c r="B224" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C224" t="s">
-        <v>1034</v>
+        <v>1085</v>
       </c>
       <c r="D224" t="s">
-        <v>1035</v>
+        <v>970</v>
       </c>
       <c r="E224" t="s">
-        <v>1036</v>
+        <v>971</v>
       </c>
       <c r="F224" t="s">
         <v>7</v>
@@ -8129,13 +8159,16 @@
         <v>9</v>
       </c>
       <c r="B225" t="s">
-        <v>492</v>
+        <v>1012</v>
+      </c>
+      <c r="C225" t="s">
+        <v>1013</v>
       </c>
       <c r="D225" t="s">
-        <v>192</v>
+        <v>1014</v>
       </c>
       <c r="E225" t="s">
-        <v>792</v>
+        <v>1015</v>
       </c>
       <c r="F225" t="s">
         <v>7</v>
@@ -8149,16 +8182,16 @@
         <v>9</v>
       </c>
       <c r="B226" t="s">
-        <v>1073</v>
+        <v>485</v>
       </c>
       <c r="D226" t="s">
-        <v>1074</v>
+        <v>189</v>
       </c>
       <c r="E226" t="s">
-        <v>1075</v>
+        <v>780</v>
       </c>
       <c r="F226" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G226" t="s">
         <v>8</v>
@@ -8169,16 +8202,16 @@
         <v>9</v>
       </c>
       <c r="B227" t="s">
-        <v>493</v>
+        <v>1047</v>
       </c>
       <c r="D227" t="s">
-        <v>193</v>
+        <v>1048</v>
       </c>
       <c r="E227" t="s">
-        <v>793</v>
+        <v>1049</v>
       </c>
       <c r="F227" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G227" t="s">
         <v>8</v>
@@ -8189,13 +8222,13 @@
         <v>9</v>
       </c>
       <c r="B228" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="D228" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E228" t="s">
-        <v>794</v>
+        <v>781</v>
       </c>
       <c r="F228" t="s">
         <v>7</v>
@@ -8209,16 +8242,16 @@
         <v>9</v>
       </c>
       <c r="B229" t="s">
-        <v>1037</v>
+        <v>487</v>
       </c>
       <c r="D229" t="s">
-        <v>1038</v>
+        <v>191</v>
       </c>
       <c r="E229" t="s">
-        <v>1039</v>
+        <v>782</v>
       </c>
       <c r="F229" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G229" t="s">
         <v>8</v>
@@ -8229,16 +8262,16 @@
         <v>9</v>
       </c>
       <c r="B230" t="s">
-        <v>495</v>
+        <v>1016</v>
       </c>
       <c r="D230" t="s">
-        <v>195</v>
+        <v>1017</v>
       </c>
       <c r="E230" t="s">
-        <v>795</v>
+        <v>1018</v>
       </c>
       <c r="F230" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G230" t="s">
         <v>8</v>
@@ -8249,13 +8282,13 @@
         <v>9</v>
       </c>
       <c r="B231" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="D231" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E231" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="F231" t="s">
         <v>7</v>
@@ -8269,13 +8302,13 @@
         <v>9</v>
       </c>
       <c r="B232" t="s">
-        <v>497</v>
+        <v>1086</v>
       </c>
       <c r="D232" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E232" t="s">
-        <v>797</v>
+        <v>784</v>
       </c>
       <c r="F232" t="s">
         <v>7</v>
@@ -8289,13 +8322,13 @@
         <v>9</v>
       </c>
       <c r="B233" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="D233" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E233" t="s">
-        <v>798</v>
+        <v>785</v>
       </c>
       <c r="F233" t="s">
         <v>7</v>
@@ -8309,13 +8342,13 @@
         <v>9</v>
       </c>
       <c r="B234" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="D234" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E234" t="s">
-        <v>799</v>
+        <v>786</v>
       </c>
       <c r="F234" t="s">
         <v>7</v>
@@ -8329,13 +8362,13 @@
         <v>9</v>
       </c>
       <c r="B235" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="D235" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E235" t="s">
-        <v>800</v>
+        <v>787</v>
       </c>
       <c r="F235" t="s">
         <v>7</v>
@@ -8349,13 +8382,13 @@
         <v>9</v>
       </c>
       <c r="B236" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="D236" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E236" t="s">
-        <v>801</v>
+        <v>788</v>
       </c>
       <c r="F236" t="s">
         <v>7</v>
@@ -8369,16 +8402,13 @@
         <v>9</v>
       </c>
       <c r="B237" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C237" t="s">
-        <v>1041</v>
+        <v>493</v>
       </c>
       <c r="D237" t="s">
-        <v>1042</v>
+        <v>198</v>
       </c>
       <c r="E237" t="s">
-        <v>1043</v>
+        <v>789</v>
       </c>
       <c r="F237" t="s">
         <v>7</v>
@@ -8392,13 +8422,16 @@
         <v>9</v>
       </c>
       <c r="B238" t="s">
-        <v>502</v>
+        <v>1019</v>
+      </c>
+      <c r="C238" t="s">
+        <v>1020</v>
       </c>
       <c r="D238" t="s">
-        <v>202</v>
+        <v>1021</v>
       </c>
       <c r="E238" t="s">
-        <v>802</v>
+        <v>1022</v>
       </c>
       <c r="F238" t="s">
         <v>7</v>
@@ -8412,13 +8445,13 @@
         <v>9</v>
       </c>
       <c r="B239" t="s">
-        <v>1076</v>
+        <v>494</v>
       </c>
       <c r="D239" t="s">
-        <v>1077</v>
+        <v>199</v>
       </c>
       <c r="E239" t="s">
-        <v>1078</v>
+        <v>790</v>
       </c>
       <c r="F239" t="s">
         <v>7</v>
@@ -8432,16 +8465,16 @@
         <v>9</v>
       </c>
       <c r="B240" t="s">
-        <v>503</v>
+        <v>1087</v>
       </c>
       <c r="D240" t="s">
-        <v>203</v>
+        <v>1088</v>
       </c>
       <c r="E240" t="s">
-        <v>803</v>
+        <v>1089</v>
       </c>
       <c r="F240" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G240" t="s">
         <v>8</v>
@@ -8452,13 +8485,13 @@
         <v>9</v>
       </c>
       <c r="B241" t="s">
-        <v>504</v>
+        <v>1050</v>
       </c>
       <c r="D241" t="s">
-        <v>204</v>
+        <v>1051</v>
       </c>
       <c r="E241" t="s">
-        <v>804</v>
+        <v>1052</v>
       </c>
       <c r="F241" t="s">
         <v>7</v>
@@ -8472,16 +8505,16 @@
         <v>9</v>
       </c>
       <c r="B242" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="D242" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E242" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
       <c r="F242" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G242" t="s">
         <v>8</v>
@@ -8492,13 +8525,13 @@
         <v>9</v>
       </c>
       <c r="B243" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D243" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E243" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="F243" t="s">
         <v>7</v>
@@ -8512,13 +8545,13 @@
         <v>9</v>
       </c>
       <c r="B244" t="s">
-        <v>507</v>
+        <v>1090</v>
       </c>
       <c r="D244" t="s">
-        <v>207</v>
+        <v>1091</v>
       </c>
       <c r="E244" t="s">
-        <v>807</v>
+        <v>1092</v>
       </c>
       <c r="F244" t="s">
         <v>7</v>
@@ -8532,16 +8565,13 @@
         <v>9</v>
       </c>
       <c r="B245" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C245" t="s">
-        <v>1080</v>
+        <v>497</v>
       </c>
       <c r="D245" t="s">
-        <v>1081</v>
+        <v>202</v>
       </c>
       <c r="E245" t="s">
-        <v>1082</v>
+        <v>793</v>
       </c>
       <c r="F245" t="s">
         <v>7</v>
@@ -8555,13 +8585,13 @@
         <v>9</v>
       </c>
       <c r="B246" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="D246" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E246" t="s">
-        <v>808</v>
+        <v>794</v>
       </c>
       <c r="F246" t="s">
         <v>7</v>
@@ -8575,13 +8605,16 @@
         <v>9</v>
       </c>
       <c r="B247" t="s">
-        <v>1044</v>
+        <v>1053</v>
+      </c>
+      <c r="C247" t="s">
+        <v>1054</v>
       </c>
       <c r="D247" t="s">
-        <v>1045</v>
+        <v>1055</v>
       </c>
       <c r="E247" t="s">
-        <v>1046</v>
+        <v>1056</v>
       </c>
       <c r="F247" t="s">
         <v>7</v>
@@ -8595,13 +8628,13 @@
         <v>9</v>
       </c>
       <c r="B248" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="D248" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E248" t="s">
-        <v>809</v>
+        <v>795</v>
       </c>
       <c r="F248" t="s">
         <v>7</v>
@@ -8615,13 +8648,13 @@
         <v>9</v>
       </c>
       <c r="B249" t="s">
-        <v>510</v>
+        <v>1023</v>
       </c>
       <c r="D249" t="s">
-        <v>210</v>
+        <v>1024</v>
       </c>
       <c r="E249" t="s">
-        <v>810</v>
+        <v>1025</v>
       </c>
       <c r="F249" t="s">
         <v>7</v>
@@ -8635,13 +8668,13 @@
         <v>9</v>
       </c>
       <c r="B250" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="D250" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E250" t="s">
-        <v>811</v>
+        <v>796</v>
       </c>
       <c r="F250" t="s">
         <v>7</v>
@@ -8655,13 +8688,13 @@
         <v>9</v>
       </c>
       <c r="B251" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="D251" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E251" t="s">
-        <v>812</v>
+        <v>797</v>
       </c>
       <c r="F251" t="s">
         <v>7</v>
@@ -8675,13 +8708,13 @@
         <v>9</v>
       </c>
       <c r="B252" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="D252" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E252" t="s">
-        <v>813</v>
+        <v>798</v>
       </c>
       <c r="F252" t="s">
         <v>7</v>
@@ -8695,13 +8728,13 @@
         <v>9</v>
       </c>
       <c r="B253" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="D253" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E253" t="s">
-        <v>814</v>
+        <v>799</v>
       </c>
       <c r="F253" t="s">
         <v>7</v>
@@ -8715,13 +8748,13 @@
         <v>9</v>
       </c>
       <c r="B254" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="D254" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E254" t="s">
-        <v>815</v>
+        <v>800</v>
       </c>
       <c r="F254" t="s">
         <v>7</v>
@@ -8735,13 +8768,13 @@
         <v>9</v>
       </c>
       <c r="B255" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="D255" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E255" t="s">
-        <v>816</v>
+        <v>801</v>
       </c>
       <c r="F255" t="s">
         <v>7</v>
@@ -8755,13 +8788,13 @@
         <v>9</v>
       </c>
       <c r="B256" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="D256" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E256" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="F256" t="s">
         <v>7</v>
@@ -8775,13 +8808,13 @@
         <v>9</v>
       </c>
       <c r="B257" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="D257" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E257" t="s">
-        <v>818</v>
+        <v>803</v>
       </c>
       <c r="F257" t="s">
         <v>7</v>
@@ -8795,13 +8828,13 @@
         <v>9</v>
       </c>
       <c r="B258" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="D258" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E258" t="s">
-        <v>819</v>
+        <v>804</v>
       </c>
       <c r="F258" t="s">
         <v>7</v>
@@ -8815,13 +8848,13 @@
         <v>9</v>
       </c>
       <c r="B259" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="D259" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="E259" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="F259" t="s">
         <v>7</v>
@@ -8835,16 +8868,16 @@
         <v>9</v>
       </c>
       <c r="B260" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="D260" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="E260" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="F260" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G260" t="s">
         <v>8</v>
@@ -8855,13 +8888,13 @@
         <v>9</v>
       </c>
       <c r="B261" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="D261" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E261" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="F261" t="s">
         <v>7</v>
@@ -8875,16 +8908,16 @@
         <v>9</v>
       </c>
       <c r="B262" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="D262" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E262" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="F262" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G262" t="s">
         <v>8</v>
@@ -8895,13 +8928,13 @@
         <v>9</v>
       </c>
       <c r="B263" t="s">
-        <v>524</v>
+        <v>1093</v>
       </c>
       <c r="D263" t="s">
-        <v>224</v>
+        <v>1094</v>
       </c>
       <c r="E263" t="s">
-        <v>824</v>
+        <v>1095</v>
       </c>
       <c r="F263" t="s">
         <v>7</v>
@@ -8915,13 +8948,13 @@
         <v>9</v>
       </c>
       <c r="B264" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="D264" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E264" t="s">
-        <v>825</v>
+        <v>809</v>
       </c>
       <c r="F264" t="s">
         <v>7</v>
@@ -8935,13 +8968,13 @@
         <v>9</v>
       </c>
       <c r="B265" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="D265" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E265" t="s">
-        <v>826</v>
+        <v>810</v>
       </c>
       <c r="F265" t="s">
         <v>7</v>
@@ -8955,13 +8988,13 @@
         <v>9</v>
       </c>
       <c r="B266" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="D266" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E266" t="s">
-        <v>827</v>
+        <v>811</v>
       </c>
       <c r="F266" t="s">
         <v>7</v>
@@ -8975,16 +9008,16 @@
         <v>9</v>
       </c>
       <c r="B267" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="D267" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E267" t="s">
-        <v>828</v>
+        <v>812</v>
       </c>
       <c r="F267" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G267" t="s">
         <v>8</v>
@@ -8995,13 +9028,13 @@
         <v>9</v>
       </c>
       <c r="B268" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="D268" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="E268" t="s">
-        <v>829</v>
+        <v>813</v>
       </c>
       <c r="F268" t="s">
         <v>7</v>
@@ -9015,13 +9048,13 @@
         <v>9</v>
       </c>
       <c r="B269" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="D269" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="E269" t="s">
-        <v>830</v>
+        <v>814</v>
       </c>
       <c r="F269" t="s">
         <v>7</v>
@@ -9035,16 +9068,16 @@
         <v>9</v>
       </c>
       <c r="B270" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="D270" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E270" t="s">
-        <v>831</v>
+        <v>815</v>
       </c>
       <c r="F270" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G270" t="s">
         <v>8</v>
@@ -9055,13 +9088,13 @@
         <v>9</v>
       </c>
       <c r="B271" t="s">
-        <v>1083</v>
+        <v>520</v>
       </c>
       <c r="D271" t="s">
-        <v>1084</v>
+        <v>225</v>
       </c>
       <c r="E271" t="s">
-        <v>1085</v>
+        <v>816</v>
       </c>
       <c r="F271" t="s">
         <v>7</v>
@@ -9075,13 +9108,13 @@
         <v>9</v>
       </c>
       <c r="B272" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="D272" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="E272" t="s">
-        <v>832</v>
+        <v>817</v>
       </c>
       <c r="F272" t="s">
         <v>7</v>
@@ -9095,13 +9128,13 @@
         <v>9</v>
       </c>
       <c r="B273" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="D273" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="E273" t="s">
-        <v>833</v>
+        <v>818</v>
       </c>
       <c r="F273" t="s">
         <v>7</v>
@@ -9115,13 +9148,13 @@
         <v>9</v>
       </c>
       <c r="B274" t="s">
-        <v>534</v>
+        <v>1057</v>
       </c>
       <c r="D274" t="s">
-        <v>234</v>
+        <v>1058</v>
       </c>
       <c r="E274" t="s">
-        <v>834</v>
+        <v>1059</v>
       </c>
       <c r="F274" t="s">
         <v>7</v>
@@ -9135,13 +9168,13 @@
         <v>9</v>
       </c>
       <c r="B275" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="D275" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E275" t="s">
-        <v>835</v>
+        <v>819</v>
       </c>
       <c r="F275" t="s">
         <v>7</v>
@@ -9155,13 +9188,13 @@
         <v>9</v>
       </c>
       <c r="B276" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="D276" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E276" t="s">
-        <v>836</v>
+        <v>820</v>
       </c>
       <c r="F276" t="s">
         <v>7</v>
@@ -9175,13 +9208,13 @@
         <v>9</v>
       </c>
       <c r="B277" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="D277" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E277" t="s">
-        <v>837</v>
+        <v>821</v>
       </c>
       <c r="F277" t="s">
         <v>7</v>
@@ -9195,13 +9228,13 @@
         <v>9</v>
       </c>
       <c r="B278" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="D278" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="E278" t="s">
-        <v>838</v>
+        <v>822</v>
       </c>
       <c r="F278" t="s">
         <v>7</v>
@@ -9215,13 +9248,13 @@
         <v>9</v>
       </c>
       <c r="B279" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="D279" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E279" t="s">
-        <v>839</v>
+        <v>823</v>
       </c>
       <c r="F279" t="s">
         <v>7</v>
@@ -9235,13 +9268,13 @@
         <v>9</v>
       </c>
       <c r="B280" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="D280" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E280" t="s">
-        <v>840</v>
+        <v>824</v>
       </c>
       <c r="F280" t="s">
         <v>7</v>
@@ -9255,13 +9288,13 @@
         <v>9</v>
       </c>
       <c r="B281" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="D281" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="E281" t="s">
-        <v>841</v>
+        <v>825</v>
       </c>
       <c r="F281" t="s">
         <v>7</v>
@@ -9275,13 +9308,13 @@
         <v>9</v>
       </c>
       <c r="B282" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="D282" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E282" t="s">
-        <v>842</v>
+        <v>826</v>
       </c>
       <c r="F282" t="s">
         <v>7</v>
@@ -9295,13 +9328,13 @@
         <v>9</v>
       </c>
       <c r="B283" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="D283" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E283" t="s">
-        <v>843</v>
+        <v>827</v>
       </c>
       <c r="F283" t="s">
         <v>7</v>
@@ -9315,13 +9348,13 @@
         <v>9</v>
       </c>
       <c r="B284" t="s">
-        <v>983</v>
+        <v>532</v>
       </c>
       <c r="D284" t="s">
-        <v>984</v>
+        <v>237</v>
       </c>
       <c r="E284" t="s">
-        <v>985</v>
+        <v>828</v>
       </c>
       <c r="F284" t="s">
         <v>7</v>
@@ -9335,13 +9368,13 @@
         <v>9</v>
       </c>
       <c r="B285" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="D285" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E285" t="s">
-        <v>844</v>
+        <v>829</v>
       </c>
       <c r="F285" t="s">
         <v>7</v>
@@ -9355,13 +9388,13 @@
         <v>9</v>
       </c>
       <c r="B286" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="D286" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E286" t="s">
-        <v>845</v>
+        <v>830</v>
       </c>
       <c r="F286" t="s">
         <v>7</v>
@@ -9375,13 +9408,13 @@
         <v>9</v>
       </c>
       <c r="B287" t="s">
-        <v>546</v>
+        <v>967</v>
       </c>
       <c r="D287" t="s">
-        <v>246</v>
+        <v>968</v>
       </c>
       <c r="E287" t="s">
-        <v>846</v>
+        <v>969</v>
       </c>
       <c r="F287" t="s">
         <v>7</v>
@@ -9395,13 +9428,13 @@
         <v>9</v>
       </c>
       <c r="B288" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="D288" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="E288" t="s">
-        <v>847</v>
+        <v>831</v>
       </c>
       <c r="F288" t="s">
         <v>7</v>
@@ -9415,16 +9448,16 @@
         <v>9</v>
       </c>
       <c r="B289" t="s">
-        <v>989</v>
+        <v>536</v>
       </c>
       <c r="D289" t="s">
-        <v>990</v>
+        <v>241</v>
       </c>
       <c r="E289" t="s">
-        <v>991</v>
+        <v>832</v>
       </c>
       <c r="F289" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G289" t="s">
         <v>8</v>
@@ -9435,13 +9468,13 @@
         <v>9</v>
       </c>
       <c r="B290" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="D290" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E290" t="s">
-        <v>848</v>
+        <v>833</v>
       </c>
       <c r="F290" t="s">
         <v>7</v>
@@ -9455,13 +9488,13 @@
         <v>9</v>
       </c>
       <c r="B291" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="D291" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E291" t="s">
-        <v>849</v>
+        <v>834</v>
       </c>
       <c r="F291" t="s">
         <v>7</v>
@@ -9475,16 +9508,16 @@
         <v>9</v>
       </c>
       <c r="B292" t="s">
-        <v>550</v>
+        <v>972</v>
       </c>
       <c r="D292" t="s">
-        <v>250</v>
+        <v>973</v>
       </c>
       <c r="E292" t="s">
-        <v>850</v>
+        <v>974</v>
       </c>
       <c r="F292" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G292" t="s">
         <v>8</v>
@@ -9495,13 +9528,13 @@
         <v>9</v>
       </c>
       <c r="B293" t="s">
-        <v>995</v>
+        <v>539</v>
       </c>
       <c r="D293" t="s">
-        <v>996</v>
+        <v>244</v>
       </c>
       <c r="E293" t="s">
-        <v>997</v>
+        <v>835</v>
       </c>
       <c r="F293" t="s">
         <v>7</v>
@@ -9515,13 +9548,13 @@
         <v>9</v>
       </c>
       <c r="B294" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="D294" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E294" t="s">
-        <v>851</v>
+        <v>836</v>
       </c>
       <c r="F294" t="s">
         <v>7</v>
@@ -9535,13 +9568,13 @@
         <v>9</v>
       </c>
       <c r="B295" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="D295" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="E295" t="s">
-        <v>852</v>
+        <v>837</v>
       </c>
       <c r="F295" t="s">
         <v>7</v>
@@ -9555,13 +9588,13 @@
         <v>9</v>
       </c>
       <c r="B296" t="s">
-        <v>553</v>
+        <v>977</v>
       </c>
       <c r="D296" t="s">
-        <v>253</v>
+        <v>978</v>
       </c>
       <c r="E296" t="s">
-        <v>853</v>
+        <v>979</v>
       </c>
       <c r="F296" t="s">
         <v>7</v>
@@ -9575,13 +9608,13 @@
         <v>9</v>
       </c>
       <c r="B297" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="D297" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E297" t="s">
-        <v>854</v>
+        <v>838</v>
       </c>
       <c r="F297" t="s">
         <v>7</v>
@@ -9595,13 +9628,13 @@
         <v>9</v>
       </c>
       <c r="B298" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="D298" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E298" t="s">
-        <v>855</v>
+        <v>839</v>
       </c>
       <c r="F298" t="s">
         <v>7</v>
@@ -9615,13 +9648,13 @@
         <v>9</v>
       </c>
       <c r="B299" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="D299" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="E299" t="s">
-        <v>856</v>
+        <v>840</v>
       </c>
       <c r="F299" t="s">
         <v>7</v>
@@ -9635,13 +9668,13 @@
         <v>9</v>
       </c>
       <c r="B300" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="D300" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="E300" t="s">
-        <v>857</v>
+        <v>841</v>
       </c>
       <c r="F300" t="s">
         <v>7</v>
@@ -9655,13 +9688,13 @@
         <v>9</v>
       </c>
       <c r="B301" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="D301" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="E301" t="s">
-        <v>858</v>
+        <v>842</v>
       </c>
       <c r="F301" t="s">
         <v>7</v>
@@ -9675,13 +9708,13 @@
         <v>9</v>
       </c>
       <c r="B302" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D302" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E302" t="s">
-        <v>859</v>
+        <v>843</v>
       </c>
       <c r="F302" t="s">
         <v>7</v>
@@ -9695,16 +9728,16 @@
         <v>9</v>
       </c>
       <c r="B303" t="s">
-        <v>992</v>
+        <v>548</v>
       </c>
       <c r="D303" t="s">
-        <v>993</v>
+        <v>253</v>
       </c>
       <c r="E303" t="s">
-        <v>994</v>
+        <v>844</v>
       </c>
       <c r="F303" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G303" t="s">
         <v>8</v>
@@ -9715,13 +9748,13 @@
         <v>9</v>
       </c>
       <c r="B304" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="D304" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E304" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="F304" t="s">
         <v>7</v>
@@ -9735,13 +9768,13 @@
         <v>9</v>
       </c>
       <c r="B305" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="D305" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="E305" t="s">
-        <v>861</v>
+        <v>846</v>
       </c>
       <c r="F305" t="s">
         <v>7</v>
@@ -9755,16 +9788,16 @@
         <v>9</v>
       </c>
       <c r="B306" t="s">
-        <v>562</v>
+        <v>1096</v>
       </c>
       <c r="D306" t="s">
-        <v>262</v>
+        <v>975</v>
       </c>
       <c r="E306" t="s">
-        <v>862</v>
+        <v>976</v>
       </c>
       <c r="F306" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G306" t="s">
         <v>8</v>
@@ -9775,13 +9808,13 @@
         <v>9</v>
       </c>
       <c r="B307" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="D307" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E307" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="F307" t="s">
         <v>7</v>
@@ -9795,13 +9828,13 @@
         <v>9</v>
       </c>
       <c r="B308" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="D308" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E308" t="s">
-        <v>864</v>
+        <v>848</v>
       </c>
       <c r="F308" t="s">
         <v>7</v>
@@ -9815,13 +9848,13 @@
         <v>9</v>
       </c>
       <c r="B309" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D309" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="E309" t="s">
-        <v>865</v>
+        <v>849</v>
       </c>
       <c r="F309" t="s">
         <v>7</v>
@@ -9835,13 +9868,13 @@
         <v>9</v>
       </c>
       <c r="B310" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="D310" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E310" t="s">
-        <v>866</v>
+        <v>850</v>
       </c>
       <c r="F310" t="s">
         <v>7</v>
@@ -9855,13 +9888,13 @@
         <v>9</v>
       </c>
       <c r="B311" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="D311" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E311" t="s">
-        <v>867</v>
+        <v>851</v>
       </c>
       <c r="F311" t="s">
         <v>7</v>
@@ -9875,13 +9908,13 @@
         <v>9</v>
       </c>
       <c r="B312" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="D312" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="E312" t="s">
-        <v>868</v>
+        <v>852</v>
       </c>
       <c r="F312" t="s">
         <v>7</v>
@@ -9895,13 +9928,13 @@
         <v>9</v>
       </c>
       <c r="B313" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="D313" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="E313" t="s">
-        <v>869</v>
+        <v>853</v>
       </c>
       <c r="F313" t="s">
         <v>7</v>
@@ -9915,13 +9948,13 @@
         <v>9</v>
       </c>
       <c r="B314" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="D314" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E314" t="s">
-        <v>870</v>
+        <v>854</v>
       </c>
       <c r="F314" t="s">
         <v>7</v>
@@ -9935,13 +9968,13 @@
         <v>9</v>
       </c>
       <c r="B315" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="D315" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E315" t="s">
-        <v>871</v>
+        <v>855</v>
       </c>
       <c r="F315" t="s">
         <v>7</v>
@@ -9955,13 +9988,13 @@
         <v>9</v>
       </c>
       <c r="B316" t="s">
-        <v>1086</v>
+        <v>560</v>
       </c>
       <c r="D316" t="s">
-        <v>1087</v>
+        <v>265</v>
       </c>
       <c r="E316" t="s">
-        <v>1088</v>
+        <v>856</v>
       </c>
       <c r="F316" t="s">
         <v>7</v>
@@ -9975,13 +10008,13 @@
         <v>9</v>
       </c>
       <c r="B317" t="s">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="D317" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E317" t="s">
-        <v>872</v>
+        <v>857</v>
       </c>
       <c r="F317" t="s">
         <v>7</v>
@@ -9995,13 +10028,13 @@
         <v>9</v>
       </c>
       <c r="B318" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="D318" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E318" t="s">
-        <v>873</v>
+        <v>858</v>
       </c>
       <c r="F318" t="s">
         <v>7</v>
@@ -10015,13 +10048,13 @@
         <v>9</v>
       </c>
       <c r="B319" t="s">
-        <v>574</v>
+        <v>1060</v>
       </c>
       <c r="D319" t="s">
-        <v>274</v>
+        <v>1061</v>
       </c>
       <c r="E319" t="s">
-        <v>874</v>
+        <v>1062</v>
       </c>
       <c r="F319" t="s">
         <v>7</v>
@@ -10035,13 +10068,13 @@
         <v>9</v>
       </c>
       <c r="B320" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="D320" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E320" t="s">
-        <v>875</v>
+        <v>859</v>
       </c>
       <c r="F320" t="s">
         <v>7</v>
@@ -10055,13 +10088,13 @@
         <v>9</v>
       </c>
       <c r="B321" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="D321" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="E321" t="s">
-        <v>876</v>
+        <v>860</v>
       </c>
       <c r="F321" t="s">
         <v>7</v>
@@ -10075,13 +10108,13 @@
         <v>9</v>
       </c>
       <c r="B322" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="D322" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="E322" t="s">
-        <v>877</v>
+        <v>861</v>
       </c>
       <c r="F322" t="s">
         <v>7</v>
@@ -10095,13 +10128,13 @@
         <v>9</v>
       </c>
       <c r="B323" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="D323" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="E323" t="s">
-        <v>878</v>
+        <v>862</v>
       </c>
       <c r="F323" t="s">
         <v>7</v>
@@ -10115,13 +10148,13 @@
         <v>9</v>
       </c>
       <c r="B324" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="D324" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="E324" t="s">
-        <v>879</v>
+        <v>863</v>
       </c>
       <c r="F324" t="s">
         <v>7</v>
@@ -10135,13 +10168,13 @@
         <v>9</v>
       </c>
       <c r="B325" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="D325" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="E325" t="s">
-        <v>880</v>
+        <v>864</v>
       </c>
       <c r="F325" t="s">
         <v>7</v>
@@ -10155,13 +10188,13 @@
         <v>9</v>
       </c>
       <c r="B326" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="D326" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="E326" t="s">
-        <v>881</v>
+        <v>865</v>
       </c>
       <c r="F326" t="s">
         <v>7</v>
@@ -10175,13 +10208,13 @@
         <v>9</v>
       </c>
       <c r="B327" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="D327" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E327" t="s">
-        <v>882</v>
+        <v>866</v>
       </c>
       <c r="F327" t="s">
         <v>7</v>
@@ -10195,13 +10228,13 @@
         <v>9</v>
       </c>
       <c r="B328" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="D328" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="E328" t="s">
-        <v>883</v>
+        <v>867</v>
       </c>
       <c r="F328" t="s">
         <v>7</v>
@@ -10215,13 +10248,13 @@
         <v>9</v>
       </c>
       <c r="B329" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="D329" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E329" t="s">
-        <v>884</v>
+        <v>868</v>
       </c>
       <c r="F329" t="s">
         <v>7</v>
@@ -10235,16 +10268,16 @@
         <v>9</v>
       </c>
       <c r="B330" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="D330" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E330" t="s">
-        <v>885</v>
+        <v>869</v>
       </c>
       <c r="F330" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G330" t="s">
         <v>8</v>
@@ -10255,13 +10288,13 @@
         <v>9</v>
       </c>
       <c r="B331" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="D331" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E331" t="s">
-        <v>886</v>
+        <v>870</v>
       </c>
       <c r="F331" t="s">
         <v>7</v>
@@ -10275,13 +10308,13 @@
         <v>9</v>
       </c>
       <c r="B332" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="D332" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E332" t="s">
-        <v>887</v>
+        <v>871</v>
       </c>
       <c r="F332" t="s">
         <v>7</v>
@@ -10295,16 +10328,16 @@
         <v>9</v>
       </c>
       <c r="B333" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="D333" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E333" t="s">
-        <v>888</v>
+        <v>872</v>
       </c>
       <c r="F333" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G333" t="s">
         <v>8</v>
@@ -10315,13 +10348,13 @@
         <v>9</v>
       </c>
       <c r="B334" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="D334" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E334" t="s">
-        <v>889</v>
+        <v>873</v>
       </c>
       <c r="F334" t="s">
         <v>7</v>
@@ -10335,13 +10368,13 @@
         <v>9</v>
       </c>
       <c r="B335" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="D335" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="E335" t="s">
-        <v>890</v>
+        <v>874</v>
       </c>
       <c r="F335" t="s">
         <v>7</v>
@@ -10355,13 +10388,13 @@
         <v>9</v>
       </c>
       <c r="B336" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="D336" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="E336" t="s">
-        <v>891</v>
+        <v>875</v>
       </c>
       <c r="F336" t="s">
         <v>7</v>
@@ -10375,13 +10408,13 @@
         <v>9</v>
       </c>
       <c r="B337" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="D337" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E337" t="s">
-        <v>892</v>
+        <v>876</v>
       </c>
       <c r="F337" t="s">
         <v>7</v>
@@ -10395,13 +10428,13 @@
         <v>9</v>
       </c>
       <c r="B338" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="D338" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="E338" t="s">
-        <v>893</v>
+        <v>877</v>
       </c>
       <c r="F338" t="s">
         <v>7</v>
@@ -10415,13 +10448,13 @@
         <v>9</v>
       </c>
       <c r="B339" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="D339" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="E339" t="s">
-        <v>894</v>
+        <v>878</v>
       </c>
       <c r="F339" t="s">
         <v>7</v>
@@ -10435,16 +10468,16 @@
         <v>9</v>
       </c>
       <c r="B340" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="D340" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="E340" t="s">
-        <v>895</v>
+        <v>879</v>
       </c>
       <c r="F340" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G340" t="s">
         <v>8</v>
@@ -10455,13 +10488,13 @@
         <v>9</v>
       </c>
       <c r="B341" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="D341" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="E341" t="s">
-        <v>896</v>
+        <v>880</v>
       </c>
       <c r="F341" t="s">
         <v>7</v>
@@ -10475,13 +10508,13 @@
         <v>9</v>
       </c>
       <c r="B342" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="D342" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="E342" t="s">
-        <v>897</v>
+        <v>881</v>
       </c>
       <c r="F342" t="s">
         <v>7</v>
@@ -10495,19 +10528,16 @@
         <v>9</v>
       </c>
       <c r="B343" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C343" t="s">
-        <v>1002</v>
+        <v>586</v>
       </c>
       <c r="D343" t="s">
-        <v>1003</v>
+        <v>291</v>
       </c>
       <c r="E343" t="s">
-        <v>1004</v>
+        <v>882</v>
       </c>
       <c r="F343" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G343" t="s">
         <v>8</v>
@@ -10518,13 +10548,13 @@
         <v>9</v>
       </c>
       <c r="B344" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D344" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="E344" t="s">
-        <v>898</v>
+        <v>883</v>
       </c>
       <c r="F344" t="s">
         <v>7</v>
@@ -10538,16 +10568,16 @@
         <v>9</v>
       </c>
       <c r="B345" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="D345" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E345" t="s">
-        <v>899</v>
+        <v>884</v>
       </c>
       <c r="F345" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G345" t="s">
         <v>8</v>
@@ -10558,16 +10588,19 @@
         <v>9</v>
       </c>
       <c r="B346" t="s">
-        <v>1047</v>
+        <v>983</v>
+      </c>
+      <c r="C346" t="s">
+        <v>984</v>
       </c>
       <c r="D346" t="s">
-        <v>1048</v>
+        <v>985</v>
       </c>
       <c r="E346" t="s">
-        <v>1049</v>
+        <v>986</v>
       </c>
       <c r="F346" t="s">
-        <v>910</v>
+        <v>7</v>
       </c>
       <c r="G346" t="s">
         <v>8</v>
@@ -10578,13 +10611,13 @@
         <v>9</v>
       </c>
       <c r="B347" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="D347" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E347" t="s">
-        <v>900</v>
+        <v>885</v>
       </c>
       <c r="F347" t="s">
         <v>7</v>
@@ -10598,16 +10631,16 @@
         <v>9</v>
       </c>
       <c r="B348" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="D348" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E348" t="s">
-        <v>901</v>
+        <v>886</v>
       </c>
       <c r="F348" t="s">
-        <v>7</v>
+        <v>897</v>
       </c>
       <c r="G348" t="s">
         <v>8</v>
@@ -10618,13 +10651,13 @@
         <v>9</v>
       </c>
       <c r="B349" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="D349" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="E349" t="s">
-        <v>902</v>
+        <v>887</v>
       </c>
       <c r="F349" t="s">
         <v>7</v>
@@ -10638,13 +10671,13 @@
         <v>9</v>
       </c>
       <c r="B350" t="s">
-        <v>1050</v>
+        <v>592</v>
       </c>
       <c r="D350" t="s">
-        <v>1051</v>
+        <v>297</v>
       </c>
       <c r="E350" t="s">
-        <v>1052</v>
+        <v>888</v>
       </c>
       <c r="F350" t="s">
         <v>7</v>
@@ -10658,13 +10691,13 @@
         <v>9</v>
       </c>
       <c r="B351" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="D351" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="E351" t="s">
-        <v>903</v>
+        <v>889</v>
       </c>
       <c r="F351" t="s">
         <v>7</v>
@@ -10678,13 +10711,13 @@
         <v>9</v>
       </c>
       <c r="B352" t="s">
-        <v>604</v>
+        <v>1026</v>
       </c>
       <c r="D352" t="s">
-        <v>304</v>
+        <v>1027</v>
       </c>
       <c r="E352" t="s">
-        <v>904</v>
+        <v>1028</v>
       </c>
       <c r="F352" t="s">
         <v>7</v>
@@ -10698,13 +10731,13 @@
         <v>9</v>
       </c>
       <c r="B353" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="D353" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="E353" t="s">
-        <v>905</v>
+        <v>890</v>
       </c>
       <c r="F353" t="s">
         <v>7</v>
@@ -10718,13 +10751,13 @@
         <v>9</v>
       </c>
       <c r="B354" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="D354" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="E354" t="s">
-        <v>906</v>
+        <v>891</v>
       </c>
       <c r="F354" t="s">
         <v>7</v>
@@ -10738,13 +10771,13 @@
         <v>9</v>
       </c>
       <c r="B355" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="D355" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="E355" t="s">
-        <v>907</v>
+        <v>892</v>
       </c>
       <c r="F355" t="s">
         <v>7</v>
@@ -10758,16 +10791,13 @@
         <v>9</v>
       </c>
       <c r="B356" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C356" t="s">
-        <v>1005</v>
+        <v>597</v>
       </c>
       <c r="D356" t="s">
-        <v>1006</v>
+        <v>302</v>
       </c>
       <c r="E356" t="s">
-        <v>1007</v>
+        <v>893</v>
       </c>
       <c r="F356" t="s">
         <v>7</v>
@@ -10781,13 +10811,13 @@
         <v>9</v>
       </c>
       <c r="B357" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="D357" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E357" t="s">
-        <v>908</v>
+        <v>894</v>
       </c>
       <c r="F357" t="s">
         <v>7</v>
@@ -10801,18 +10831,61 @@
         <v>9</v>
       </c>
       <c r="B358" t="s">
-        <v>609</v>
+        <v>1029</v>
+      </c>
+      <c r="C358" t="s">
+        <v>987</v>
       </c>
       <c r="D358" t="s">
-        <v>309</v>
+        <v>988</v>
       </c>
       <c r="E358" t="s">
-        <v>909</v>
+        <v>989</v>
       </c>
       <c r="F358" t="s">
         <v>7</v>
       </c>
       <c r="G358" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>9</v>
+      </c>
+      <c r="B359" t="s">
+        <v>599</v>
+      </c>
+      <c r="D359" t="s">
+        <v>304</v>
+      </c>
+      <c r="E359" t="s">
+        <v>895</v>
+      </c>
+      <c r="F359" t="s">
+        <v>7</v>
+      </c>
+      <c r="G359" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>9</v>
+      </c>
+      <c r="B360" t="s">
+        <v>600</v>
+      </c>
+      <c r="D360" t="s">
+        <v>305</v>
+      </c>
+      <c r="E360" t="s">
+        <v>896</v>
+      </c>
+      <c r="F360" t="s">
+        <v>7</v>
+      </c>
+      <c r="G360" t="s">
         <v>8</v>
       </c>
     </row>
